--- a/data/trans_orig/P6712-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2012</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2012 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26260</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>53322</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77435</t>
+          <t>79010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>32093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57253</t>
+          <t>57358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89823</t>
+          <t>88065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126907</t>
+          <t>126066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188489</t>
+          <t>188538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221718</t>
+          <t>222650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117284</t>
+          <t>116552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145233</t>
+          <t>144231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316251</t>
+          <t>314977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359236</t>
+          <t>359621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>23618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51830</t>
+          <t>53091</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61230</t>
+          <t>59042</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93338</t>
+          <t>91874</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52338</t>
+          <t>51679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82234</t>
+          <t>83237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58523</t>
+          <t>58364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91903</t>
+          <t>91573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129777</t>
+          <t>133276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125062</t>
+          <t>124325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158986</t>
+          <t>158740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56423</t>
+          <t>56205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84042</t>
+          <t>82513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190043</t>
+          <t>190385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232178</t>
+          <t>234621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60407</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43209</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71721</t>
+          <t>70919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52139</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79691</t>
+          <t>79871</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65722</t>
+          <t>66548</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96600</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134054</t>
+          <t>132264</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167064</t>
+          <t>166661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>65824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85113</t>
+          <t>86034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206085</t>
+          <t>206405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>243506</t>
+          <t>244786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>24240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46720</t>
+          <t>47868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>40665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>24963</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58677</t>
+          <t>57615</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66407</t>
+          <t>65197</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100740</t>
+          <t>100594</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42669</t>
+          <t>43217</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70455</t>
+          <t>71462</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>118938</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>165376</t>
+          <t>163241</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84304</t>
+          <t>83113</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120762</t>
+          <t>118334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76778</t>
+          <t>78016</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110591</t>
+          <t>109496</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171697</t>
+          <t>171854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219970</t>
+          <t>216868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>171642</t>
+          <t>171989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>215427</t>
+          <t>215233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103755</t>
+          <t>103596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136726</t>
+          <t>138832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285356</t>
+          <t>285109</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>340527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>29365</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>26582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48167</t>
+          <t>50983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>24965</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46842</t>
+          <t>45747</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56201</t>
+          <t>57009</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>63885</t>
+          <t>63362</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>95280</t>
+          <t>95817</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51980</t>
+          <t>50430</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>32802</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58301</t>
+          <t>57723</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69216</t>
+          <t>69148</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>102157</t>
+          <t>101032</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>31574</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53790</t>
+          <t>52906</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44026</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69670</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>82395</t>
+          <t>81375</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>117528</t>
+          <t>114909</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59544</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75840</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58312</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102416</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84245</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125607</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66341</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39618</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105959</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129736</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>210</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223367</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197806</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253934</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163052</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139050</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187434</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>386419</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348875</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>420571</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334092</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303730</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370714</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>223</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243796</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214922</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>547</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>577888</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>535360</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>622905</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>678</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>732481</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>690323</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>768325</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>421</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452182</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>420656</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>484486</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1184663</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1131288</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1235484</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1415825</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1415825</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1415825</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>870</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>941520</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>941520</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>941520</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2357345</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2357345</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2357345</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>59544</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>44908</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>76263</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>42872</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>30812</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>56963</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>102416</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>83702</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>123871</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>66341</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>50221</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>82990</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>39618</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>28392</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>55327</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>105959</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>84691</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>126713</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>223367</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>198243</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>255103</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>163052</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>139925</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>187853</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>386419</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>351183</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>429729</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>334092</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>297758</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>365939</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>243796</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>216212</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>277087</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>25,89%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>29,43%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>577888</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>536587</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>625118</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>732481</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>695358</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>772978</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>51,74%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>49,11%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>54,6%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>452182</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>416587</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>482083</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>48,03%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>44,25%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>51,2%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1184663</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1131316</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1232799</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>50,25%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>47,99%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>52,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1415825</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1415825</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1415825</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>870</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>941520</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>941520</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>941520</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2357345</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2357345</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2357345</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2016</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5744,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5759,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5779,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5794,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5814,7 +5131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5829,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18590</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26179</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50889</t>
+          <t>51350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46062</t>
+          <t>45952</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55877</t>
+          <t>57046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>88507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50054</t>
+          <t>49603</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77662</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33618</t>
+          <t>32266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>55675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88870</t>
+          <t>89585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126231</t>
+          <t>125010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145462</t>
+          <t>146515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179597</t>
+          <t>180160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109858</t>
+          <t>109907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137253</t>
+          <t>140066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264906</t>
+          <t>263862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>310442</t>
+          <t>309555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20712</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>40797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>45040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73614</t>
+          <t>73692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37559</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>62168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89345</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>126623</t>
+          <t>128203</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61123</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90342</t>
+          <t>90411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>61721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104351</t>
+          <t>104439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142546</t>
+          <t>142463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75056</t>
+          <t>75156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107062</t>
+          <t>106814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>48523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75259</t>
+          <t>75568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133118</t>
+          <t>133061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175311</t>
+          <t>174852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7123,7 +6440,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7193,7 +6510,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24666</t>
+          <t>24381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>57116</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>14305</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40724</t>
+          <t>41413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65712</t>
+          <t>67866</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52048</t>
+          <t>52709</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80777</t>
+          <t>80763</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>31688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74397</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106351</t>
+          <t>108050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71656</t>
+          <t>70700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101342</t>
+          <t>101013</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>27873</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43389</t>
+          <t>43836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104660</t>
+          <t>103105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138890</t>
+          <t>138587</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51290</t>
+          <t>51479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,82 +7117,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,53%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>23293</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>16189</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>33924</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>60712</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>78176</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>5,39%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>23293</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>15866</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>34123</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>60712</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>47340</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>80220</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>35282</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60184</t>
+          <t>61162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32591</t>
+          <t>34499</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59050</t>
+          <t>59507</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75041</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110037</t>
+          <t>110949</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97193</t>
+          <t>96562</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>135890</t>
+          <t>136667</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68907</t>
+          <t>66668</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98263</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>173220</t>
+          <t>176812</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>224259</t>
+          <t>225039</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133957</t>
+          <t>131997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>174176</t>
+          <t>173622</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93476</t>
+          <t>95558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128799</t>
+          <t>130819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>239429</t>
+          <t>238832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>292658</t>
+          <t>291346</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116805</t>
+          <t>116828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155249</t>
+          <t>157812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8257,7 +7574,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>86758</t>
+          <t>89665</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122339</t>
+          <t>123868</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>213170</t>
+          <t>213845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>266775</t>
+          <t>264583</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31504</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27632</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51729</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49817</t>
+          <t>49349</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48812</t>
+          <t>50068</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79838</t>
+          <t>78753</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39677</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>44660</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>69584</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>91417</t>
+          <t>90557</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>125644</t>
+          <t>126478</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47720</t>
+          <t>47684</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39629</t>
+          <t>40165</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>64102</t>
+          <t>63963</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71043</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>103228</t>
+          <t>104457</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65784</t>
+          <t>68710</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54036</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78352</t>
+          <t>79485</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112947</t>
+          <t>113838</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68148</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86108</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57800</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76003</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125948</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104740</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150288</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123726</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102552</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>146198</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101727</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84064</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120646</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225454</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197949</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255951</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307397</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>277644</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342219</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>231</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230852</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206326</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259017</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538249</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>497543</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>582614</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392361</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>359690</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>425206</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>278864</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>250645</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308056</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>671225</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>627904</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>719732</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530689</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>494012</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566863</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>349</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366976</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337175</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399165</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>839</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>897665</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>843893</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>946042</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>68148</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>53024</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>85565</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>57800</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>44292</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>73616</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>125948</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>104618</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>148453</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>123726</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>102562</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>148351</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>101727</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>83381</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>120880</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>225454</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>197758</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>256595</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>307397</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>279019</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>340812</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>21,61%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>230852</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>204789</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>257195</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>538249</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>496699</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>580568</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>392361</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>359026</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>426156</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>278864</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>252700</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>305482</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>24,39%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>671225</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>627568</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>721072</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>27,3%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>25,53%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>29,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>530689</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>493187</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>566456</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>39,83%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>366976</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>338478</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>397393</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>35,41%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>32,66%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>38,35%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>897665</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>848427</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>945238</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>34,51%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>38,45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6712-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36240</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53322</t>
+          <t>50448</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50126</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32093</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57358</t>
+          <t>57645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88065</t>
+          <t>90238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126066</t>
+          <t>130059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188538</t>
+          <t>188577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222650</t>
+          <t>221099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116552</t>
+          <t>116801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144231</t>
+          <t>144511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>314977</t>
+          <t>314293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359621</t>
+          <t>357615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>48653</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>50812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59042</t>
+          <t>59442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91874</t>
+          <t>93126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51679</t>
+          <t>50547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83237</t>
+          <t>81062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58364</t>
+          <t>57443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91573</t>
+          <t>92564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133276</t>
+          <t>133440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124325</t>
+          <t>123012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158740</t>
+          <t>158017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56205</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82513</t>
+          <t>82982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190385</t>
+          <t>188408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>234621</t>
+          <t>232432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>24509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>33248</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58568</t>
+          <t>59037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>19882</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70919</t>
+          <t>71344</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>50566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79871</t>
+          <t>78753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66548</t>
+          <t>65699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>98126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132264</t>
+          <t>133232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166661</t>
+          <t>167540</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65824</t>
+          <t>65768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86034</t>
+          <t>85522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206405</t>
+          <t>207316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>244786</t>
+          <t>245148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24240</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47868</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>40492</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30925</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>58163</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65197</t>
+          <t>67239</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100594</t>
+          <t>101756</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43217</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71462</t>
+          <t>70738</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>119812</t>
+          <t>118390</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>163241</t>
+          <t>163204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83113</t>
+          <t>82767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118334</t>
+          <t>121057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78016</t>
+          <t>77510</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109496</t>
+          <t>110426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171854</t>
+          <t>170954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>216868</t>
+          <t>220675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>171989</t>
+          <t>174133</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>215233</t>
+          <t>216835</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103596</t>
+          <t>103852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138832</t>
+          <t>136144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285109</t>
+          <t>284585</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>340527</t>
+          <t>339014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29365</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>26157</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50983</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>24585</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39849</t>
+          <t>40494</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45747</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33315</t>
+          <t>33444</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57009</t>
+          <t>57278</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>63362</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>95817</t>
+          <t>95484</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50430</t>
+          <t>52111</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>33798</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>57723</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69148</t>
+          <t>70812</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>101032</t>
+          <t>101632</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31574</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52906</t>
+          <t>53641</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44439</t>
+          <t>43863</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>68526</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>81375</t>
+          <t>81263</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>114909</t>
+          <t>114530</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45490</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>83713</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>125607</t>
+          <t>123935</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50751</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>85568</t>
+          <t>86036</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>85882</t>
+          <t>88348</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129942</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>197806</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>253934</t>
+          <t>252250</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>139050</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>187434</t>
+          <t>188814</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>348875</t>
+          <t>347921</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>420571</t>
+          <t>425094</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>303730</t>
+          <t>302679</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>370714</t>
+          <t>367110</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>214922</t>
+          <t>218695</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>274046</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>535360</t>
+          <t>538478</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>622905</t>
+          <t>626723</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>690323</t>
+          <t>692765</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>768325</t>
+          <t>769119</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>420656</t>
+          <t>419379</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>484486</t>
+          <t>482649</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1131288</t>
+          <t>1131563</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1235484</t>
+          <t>1236458</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>26429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51350</t>
+          <t>52619</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45952</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57046</t>
+          <t>55950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88507</t>
+          <t>89091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49603</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76856</t>
+          <t>76817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55675</t>
+          <t>55773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89585</t>
+          <t>88660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125010</t>
+          <t>126160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146515</t>
+          <t>146022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180160</t>
+          <t>180722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109907</t>
+          <t>109545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140066</t>
+          <t>137680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>263862</t>
+          <t>264309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>309555</t>
+          <t>307956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40797</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>45239</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73692</t>
+          <t>74527</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37261</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62168</t>
+          <t>60803</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89345</t>
+          <t>88103</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128203</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>60157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90411</t>
+          <t>91312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>36991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61721</t>
+          <t>61267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104439</t>
+          <t>105027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142463</t>
+          <t>142154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75156</t>
+          <t>75355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106814</t>
+          <t>109188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,82 +6205,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>61361</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>50807</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>76218</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>32,44%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>40,29%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>153116</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>133446</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>176334</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>30,8%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>61361</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>48523</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>75568</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>32,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>39,95%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>153116</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>133061</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>174852</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>35,34%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>30,72%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6435,82 +6435,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5008</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>12531</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5008</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>12847</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25982</t>
+          <t>24880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33263</t>
+          <t>33092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57116</t>
+          <t>58295</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41413</t>
+          <t>40703</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67866</t>
+          <t>66243</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52709</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80763</t>
+          <t>79873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31688</t>
+          <t>31048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75511</t>
+          <t>74215</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108050</t>
+          <t>106319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70700</t>
+          <t>70865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101013</t>
+          <t>100460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>27763</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103105</t>
+          <t>105318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138587</t>
+          <t>138150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>52491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33924</t>
+          <t>34357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46220</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78176</t>
+          <t>78712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>34844</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61162</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>74061</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110949</t>
+          <t>110506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>96562</t>
+          <t>99489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136667</t>
+          <t>136997</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66668</t>
+          <t>66534</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98293</t>
+          <t>98481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>176812</t>
+          <t>175937</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>225039</t>
+          <t>225106</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131997</t>
+          <t>132137</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>173622</t>
+          <t>172909</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95558</t>
+          <t>95685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130819</t>
+          <t>130214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>238832</t>
+          <t>239058</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>291346</t>
+          <t>293493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116828</t>
+          <t>114990</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>157812</t>
+          <t>154934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>87847</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123868</t>
+          <t>122076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>213845</t>
+          <t>213912</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264583</t>
+          <t>266091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52344</t>
+          <t>51435</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49349</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50068</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>78753</t>
+          <t>78958</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>65527</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44660</t>
+          <t>44464</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69584</t>
+          <t>70088</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>90557</t>
+          <t>92654</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>126478</t>
+          <t>126377</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47684</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>39137</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>63963</t>
+          <t>63574</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71689</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>104457</t>
+          <t>104590</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42612</t>
+          <t>40678</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>68710</t>
+          <t>65775</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30774</t>
+          <t>30715</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>54230</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>79485</t>
+          <t>77477</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>113838</t>
+          <t>114413</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>54016</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>88525</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>43662</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>76003</t>
+          <t>74520</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>104740</t>
+          <t>105736</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>150288</t>
+          <t>150722</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>103918</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>146198</t>
+          <t>144669</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>84428</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>120646</t>
+          <t>123858</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>197949</t>
+          <t>196855</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>255951</t>
+          <t>257242</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>277644</t>
+          <t>275076</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>341572</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>206326</t>
+          <t>206525</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>259017</t>
+          <t>259934</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>497543</t>
+          <t>497370</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>582614</t>
+          <t>581252</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>359690</t>
+          <t>359997</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>425206</t>
+          <t>422348</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>250645</t>
+          <t>251789</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>308056</t>
+          <t>307124</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>627904</t>
+          <t>619486</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>719732</t>
+          <t>715371</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>494012</t>
+          <t>494847</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>566863</t>
+          <t>567744</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>337175</t>
+          <t>337494</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>399165</t>
+          <t>400767</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>843893</t>
+          <t>848108</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>946042</t>
+          <t>947477</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
